--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 00:42:59</t>
+          <t>2026-07-06 02:50:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 13:27:40</t>
+          <t>2026-07-06 15:34:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 15:34:52</t>
+          <t>2026-07-06 17:41:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,484 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 19:48:01</t>
+          <t>2026-07-06 21:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hartford Athletic FC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:54:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -860,7 +860,7 @@
         <v>5.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.59</v>
@@ -1022,7 +1022,7 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 21:54:08</t>
+          <t>2026-07-07 00:00:04</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
         <v>5.6</v>
@@ -1135,13 +1135,13 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
@@ -1156,13 +1156,13 @@
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1204,16 +1204,16 @@
         <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO3" t="n">
         <v>110</v>
@@ -1231,10 +1231,10 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
@@ -1276,7 +1276,7 @@
         <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 21:54:08</t>
+          <t>2026-07-07 00:00:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>5.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.59</v>
@@ -875,7 +875,7 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -887,7 +887,7 @@
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>2.14</v>
@@ -896,7 +896,7 @@
         <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.12</v>
@@ -923,7 +923,7 @@
         <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -935,10 +935,10 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AH2" t="n">
         <v>34</v>
@@ -950,22 +950,22 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
         <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AO2" t="n">
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.9</v>
@@ -974,113 +974,113 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00:04</t>
+          <t>2026-07-07 02:06:19</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
         <v>5.6</v>
@@ -1129,7 +1129,7 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1141,7 +1141,7 @@
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
@@ -1162,7 +1162,7 @@
         <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1334,7 +1334,261 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00:04</t>
+          <t>2026-07-07 02:06:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-07 02:06:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="I2" t="n">
         <v>1.68</v>
@@ -875,13 +875,13 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
@@ -893,16 +893,16 @@
         <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -917,10 +917,10 @@
         <v>7.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>22</v>
@@ -962,10 +962,10 @@
         <v>240</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.9</v>
@@ -974,46 +974,46 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
         <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5</v>
-      </c>
       <c r="BB2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
         <v>9.199999999999999</v>
@@ -1022,65 +1022,65 @@
         <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>10.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1153,76 +1153,76 @@
         <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y3" t="n">
         <v>18</v>
       </c>
-      <c r="Y3" t="n">
-        <v>20</v>
-      </c>
       <c r="Z3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL3" t="n">
         <v>48</v>
       </c>
-      <c r="AA3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
         <v>1.03</v>
@@ -1231,34 +1231,34 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1267,22 +1267,22 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,16 +1291,16 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,32 +1309,32 @@
         <v>20</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
         <v>3.75</v>
@@ -1383,10 +1383,10 @@
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
         <v>2.88</v>
@@ -1407,7 +1407,7 @@
         <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
         <v>1.89</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.68</v>
+        <v>2.96</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="BR2" t="n">
         <v>60</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="BS2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU2" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 04:12:23</t>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,132 +1097,132 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.07</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
         <v>1.03</v>
@@ -1231,34 +1231,34 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1267,22 +1267,22 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,304 +1291,812 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 04:12:23</t>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-07 06:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hartford Athletic FC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>18</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-07 06:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>23:30:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sacramento Republic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Rhode Island FC</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>2.34</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>2.66</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" t="n">
         <v>3.15</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I6" t="n">
         <v>3.75</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>3.1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K6" t="n">
         <v>3.55</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L6" t="n">
         <v>1.48</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M6" t="n">
         <v>1.1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N6" t="n">
         <v>2.88</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O6" t="n">
         <v>1.42</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P6" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q6" t="n">
         <v>2.24</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R6" t="n">
         <v>1.23</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S6" t="n">
         <v>4.3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T6" t="n">
         <v>1.9</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" t="n">
         <v>1.89</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V6" t="n">
         <v>1.36</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W6" t="n">
         <v>1.6</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X6" t="n">
         <v>12</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y6" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z6" t="n">
         <v>27</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA6" t="n">
         <v>80</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB6" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC6" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD6" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AE6" t="n">
         <v>55</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AF6" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG6" t="n">
         <v>14</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AH6" t="n">
         <v>23</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AI6" t="n">
         <v>75</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AJ6" t="n">
         <v>42</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AK6" t="n">
         <v>36</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL6" t="n">
         <v>60</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AM6" t="n">
         <v>160</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN6" t="n">
         <v>36</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO6" t="n">
         <v>65</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ6" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AU6" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AV6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AY6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AZ6" t="n">
         <v>15</v>
       </c>
-      <c r="BA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF4" t="n">
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>22</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BG6" t="n">
         <v>42</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BH6" t="n">
         <v>3.05</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BI6" t="n">
         <v>2.64</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BJ6" t="n">
         <v>11</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BK6" t="n">
         <v>8</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
         <v>5.4</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BO6" t="n">
         <v>4.1</v>
       </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>15</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>28</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="BT6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="BU6" t="n">
         <v>5</v>
       </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>22</v>
       </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>34</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>28</v>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-07-07 04:12:23</t>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,166 +857,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
         <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
         <v>4.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
         <v>210</v>
       </c>
       <c r="AN2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>2.82</v>
@@ -1028,59 +1028,59 @@
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
         <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS2" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>5.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
         <v>1.04</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1138,10 +1138,10 @@
         <v>1.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q3" t="n">
         <v>1.49</v>
@@ -1150,7 +1150,7 @@
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1389,16 +1389,16 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1419,13 +1419,13 @@
         <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
         <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1437,94 +1437,94 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AH4" t="n">
         <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AL4" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AT4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AY4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1536,7 +1536,7 @@
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,13 +1566,13 @@
         <v>4.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BV4" t="n">
         <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,127 +1610,127 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
         <v>27</v>
       </c>
-      <c r="AK5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1739,58 +1739,58 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>20</v>
       </c>
-      <c r="BT5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>36</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
@@ -1859,132 +1859,132 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rhode Island FC</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.55</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
         <v>1.03</v>
@@ -1996,32 +1996,32 @@
         <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>15</v>
       </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD6" t="n">
         <v>1.03</v>
       </c>
@@ -2029,22 +2029,22 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,34 +2053,34 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>28</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>22</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,265 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J2" t="n">
         <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -881,16 +881,16 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -905,7 +905,7 @@
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
         <v>1.32</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1111,148 +1111,148 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.06</v>
+        <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.01</v>
       </c>
-      <c r="M3" t="n">
+      <c r="AQ3" t="n">
         <v>1.01</v>
       </c>
-      <c r="N3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1.01</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1.01</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
         <v>1.03</v>
@@ -1273,68 +1273,68 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1368,61 +1368,61 @@
         <v>6.4</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
         <v>1.61</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
         <v>1.71</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W4" t="n">
         <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
         <v>9.800000000000001</v>
@@ -1431,13 +1431,13 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1446,7 +1446,7 @@
         <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH4" t="n">
         <v>34</v>
@@ -1458,70 +1458,70 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>12.5</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>10.5</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>4.1</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
         <v>3.1</v>
@@ -1640,7 +1640,7 @@
         <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>2.08</v>
@@ -1652,7 +1652,7 @@
         <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1661,16 +1661,16 @@
         <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1915,16 +1915,16 @@
         <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
         <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1945,7 +1945,7 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>75</v>
@@ -2017,7 +2017,7 @@
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,13 +866,13 @@
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
         <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -884,7 +884,7 @@
         <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
@@ -905,7 +905,7 @@
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.32</v>
@@ -917,7 +917,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
         <v>46</v>
@@ -962,13 +962,13 @@
         <v>95</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -986,34 +986,34 @@
         <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
         <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
         <v>4.7</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
@@ -1043,7 +1043,7 @@
         <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.6</v>
@@ -1052,7 +1052,7 @@
         <v>65</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
         <v>5.7</v>
@@ -1076,11 +1076,11 @@
         <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -1117,64 +1117,64 @@
         <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1186,97 +1186,97 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
         <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,41 +1300,41 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BT3" t="n">
         <v>5.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G4" t="n">
         <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1389,31 +1389,31 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.15</v>
@@ -1434,7 +1434,7 @@
         <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>12.5</v>
@@ -1452,7 +1452,7 @@
         <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1470,7 +1470,7 @@
         <v>250</v>
       </c>
       <c r="AO4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
         <v>4.1</v>
@@ -1488,7 +1488,7 @@
         <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
         <v>4</v>
@@ -1500,22 +1500,22 @@
         <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
         <v>5.4</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
         <v>5.7</v>
@@ -1527,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
         <v>2.5</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
         <v>10.5</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>4.1</v>
@@ -1569,7 +1569,7 @@
         <v>3.45</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>8.800000000000001</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -1610,121 +1610,121 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Sarasota Paradise</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.08</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
         <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>34</v>
       </c>
-      <c r="AF5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL5" t="n">
         <v>44</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>46</v>
-      </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1775,22 +1775,22 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,54 +1802,54 @@
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>20</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>15.5</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.8</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="U6" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN6" t="n">
         <v>21</v>
       </c>
-      <c r="AE6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17</v>
-      </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>10</v>
-      </c>
       <c r="BG6" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -2113,192 +2113,192 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rhode Island FC</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
         <v>26</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11</v>
-      </c>
       <c r="BK7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,34 +2307,34 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,265 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
         <v>27</v>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-07-07 10:07:56</t>
+      <c r="AO8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,13 +866,13 @@
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J2" t="n">
         <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -1135,7 +1135,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
@@ -1159,7 +1159,7 @@
         <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
         <v>1.27</v>
@@ -1174,7 +1174,7 @@
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1246,7 +1246,7 @@
         <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ3" t="n">
         <v>4</v>
@@ -1276,72 +1276,72 @@
         <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.59</v>
+        <v>1.08</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.56</v>
+        <v>1.06</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.2</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>1.14</v>
       </c>
       <c r="R4" t="n">
         <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>1.14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.12</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>80</v>
+        <v>970</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>70</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
@@ -1864,164 +1864,164 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Sarasota Paradise</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL6" t="n">
         <v>44</v>
       </c>
-      <c r="AB6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>40</v>
-      </c>
       <c r="AM6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC6" t="n">
         <v>18</v>
       </c>
-      <c r="AX6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>19</v>
-      </c>
       <c r="BD6" t="n">
         <v>1.03</v>
       </c>
@@ -2029,81 +2029,81 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>12.5</v>
       </c>
-      <c r="BG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,163 +2118,163 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="I7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
         <v>4.8</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y7" t="n">
         <v>17</v>
       </c>
-      <c r="Y7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
         <v>75</v>
       </c>
-      <c r="AF7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>140</v>
-      </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>16.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
         <v>1.03</v>
@@ -2283,40 +2283,40 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2325,32 +2325,32 @@
         <v>20</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
@@ -2367,192 +2367,192 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rhode Island FC</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK8" t="n">
         <v>26</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11</v>
-      </c>
       <c r="BK8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,34 +2561,34 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,265 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
         <v>27</v>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-07 12:14:32</t>
+      <c r="AO9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -875,7 +875,7 @@
         <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -890,7 +890,7 @@
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -968,7 +968,7 @@
         <v>3.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1180,7 +1180,7 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1189,13 +1189,13 @@
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1219,64 +1219,64 @@
         <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,28 +1288,28 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.47</v>
+        <v>3.05</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.06</v>
+        <v>1.88</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BU3" t="n">
         <v>3.35</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.42</v>
+        <v>6.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.42</v>
+        <v>2.88</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1377,28 +1377,28 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
         <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="R4" t="n">
         <v>1.26</v>
@@ -1416,7 +1416,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>6.4</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.63</v>
@@ -1649,7 +1649,7 @@
         <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
         <v>2.22</v>
@@ -1727,55 +1727,55 @@
         <v>15.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS5" t="n">
         <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
         <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
         <v>5.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
         <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
         <v>3.8</v>
@@ -1888,7 +1888,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1897,7 +1897,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
@@ -1918,7 +1918,7 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1966,7 +1966,7 @@
         <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
         <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.54</v>
@@ -2169,10 +2169,10 @@
         <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
         <v>1.65</v>
@@ -2181,19 +2181,19 @@
         <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
         <v>11.5</v>
@@ -2202,28 +2202,28 @@
         <v>14</v>
       </c>
       <c r="AE7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="n">
         <v>27</v>
       </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
         <v>75</v>
@@ -2232,19 +2232,19 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AP7" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
@@ -2253,13 +2253,13 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2268,13 +2268,13 @@
         <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
         <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
         <v>1.03</v>
@@ -2283,10 +2283,10 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="n">
         <v>4.3</v>
@@ -2307,40 +2307,40 @@
         <v>55</v>
       </c>
       <c r="BN7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
@@ -2674,10 +2674,10 @@
         <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -860,19 +860,19 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I2" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.52</v>
@@ -881,206 +881,206 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>540</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1135,7 +1135,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -1144,28 +1144,28 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1174,109 +1174,109 @@
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>1.88</v>
       </c>
       <c r="BT3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BU3" t="n">
         <v>3.35</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1407,124 +1407,124 @@
         <v>1.14</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1667,19 +1667,19 @@
         <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
         <v>970</v>
@@ -1688,13 +1688,13 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
         <v>70</v>
@@ -1724,58 +1724,58 @@
         <v>250</v>
       </c>
       <c r="AO5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1921,10 +1921,10 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -1942,7 +1942,7 @@
         <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>17.5</v>
@@ -1951,7 +1951,7 @@
         <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1963,10 +1963,10 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1975,40 +1975,40 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
@@ -2017,10 +2017,10 @@
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -2029,10 +2029,10 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -2151,7 +2151,7 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
@@ -2262,7 +2262,7 @@
         <v>18.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
         <v>11</v>
@@ -2310,7 +2310,7 @@
         <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2334,7 +2334,7 @@
         <v>18</v>
       </c>
       <c r="BW7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2423,10 +2423,10 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
         <v>1.26</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
         <v>26</v>
@@ -2713,7 +2713,7 @@
         <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
         <v>13.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>2.34</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.52</v>
@@ -881,94 +881,94 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
         <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>8.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK2" t="n">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
@@ -977,110 +977,110 @@
         <v>13</v>
       </c>
       <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G3" t="n">
         <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J3" t="n">
         <v>2.72</v>
@@ -1129,31 +1129,31 @@
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.82</v>
@@ -1162,13 +1162,13 @@
         <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
@@ -1177,10 +1177,10 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1213,64 +1213,64 @@
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="BF3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,16 +1300,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="BT3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BU3" t="n">
         <v>3.35</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -1365,217 +1365,217 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
         <v>10.5</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X4" t="n">
-        <v>500</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>500</v>
-      </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.07</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.07</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.07</v>
+        <v>5.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.07</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.07</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.06</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.07</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.07</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="n">
         <v>1.6</v>
@@ -1631,58 +1631,58 @@
         <v>1.69</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W5" t="n">
         <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AB5" t="n">
         <v>21</v>
@@ -1703,7 +1703,7 @@
         <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1712,7 +1712,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AL5" t="n">
         <v>150</v>
@@ -1721,22 +1721,22 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1745,104 +1745,104 @@
         <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BO5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>10</v>
-      </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>8.6</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1891,7 +1891,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1903,13 +1903,13 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
         <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
         <v>3.4</v>
@@ -1921,10 +1921,10 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -1936,19 +1936,19 @@
         <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
         <v>17</v>
@@ -1963,10 +1963,10 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1975,76 +1975,76 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,31 +2056,31 @@
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -2127,61 +2127,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
         <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2232,49 +2232,49 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
         <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
         <v>1.03</v>
@@ -2283,10 +2283,10 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="n">
         <v>4.3</v>
@@ -2313,7 +2313,7 @@
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
         <v>14</v>
@@ -2337,20 +2337,20 @@
         <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
         <v>18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA7" t="n">
         <v>12.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
         <v>2.02</v>
@@ -2393,13 +2393,13 @@
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -2411,7 +2411,7 @@
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
         <v>1.95</v>
@@ -2423,7 +2423,7 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.99</v>
@@ -2441,7 +2441,7 @@
         <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
         <v>130</v>
@@ -2543,16 +2543,16 @@
         <v>48</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,50 +2561,50 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2656,7 +2656,7 @@
         <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
         <v>3.2</v>
@@ -2674,7 +2674,7 @@
         <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
         <v>1.81</v>
@@ -2689,10 +2689,10 @@
         <v>1.63</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>26</v>
@@ -2701,7 +2701,7 @@
         <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2749,7 +2749,7 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
         <v>1.03</v>
@@ -2773,7 +2773,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2800,7 +2800,7 @@
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2821,7 +2821,7 @@
         <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ9" t="n">
         <v>14.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -860,79 +860,79 @@
         <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
         <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
@@ -941,16 +941,16 @@
         <v>17.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
         <v>200</v>
@@ -962,25 +962,25 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
@@ -992,95 +992,95 @@
         <v>18.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>65</v>
       </c>
-      <c r="BS2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>55</v>
-      </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
         <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.94</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.82</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>17.5</v>
@@ -1219,58 +1219,58 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BB3" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
         <v>6.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
@@ -1404,7 +1404,7 @@
         <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.54</v>
@@ -1530,55 +1530,55 @@
         <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>80</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>5.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>30</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
@@ -1637,7 +1637,7 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1646,13 +1646,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1661,13 +1661,13 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
         <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W5" t="n">
         <v>1.14</v>
@@ -1676,7 +1676,7 @@
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
@@ -1727,16 +1727,16 @@
         <v>14.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR5" t="n">
         <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1748,55 +1748,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB5" t="n">
         <v>7.4</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BT5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4</v>
-      </c>
       <c r="BU5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.6</v>
+        <v>1.89</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1987,7 +1987,7 @@
         <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS6" t="n">
         <v>5.3</v>
@@ -2017,7 +2017,7 @@
         <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -2032,19 +2032,19 @@
         <v>15.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.34</v>
@@ -2142,31 +2142,31 @@
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
         <v>1.55</v>
@@ -2178,7 +2178,7 @@
         <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>26</v>
@@ -2235,64 +2235,64 @@
         <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
         <v>12.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BN7" t="n">
         <v>6.6</v>
@@ -2322,13 +2322,13 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
         <v>18</v>
@@ -2337,20 +2337,20 @@
         <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY7" t="n">
         <v>18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
         <v>12.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -2423,7 +2423,7 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
         <v>1.99</v>
@@ -2432,7 +2432,7 @@
         <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G2" t="n">
         <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2" t="n">
         <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
         <v>1.58</v>
@@ -911,16 +911,16 @@
         <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>7.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
         <v>9.800000000000001</v>
@@ -932,28 +932,28 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ2" t="n">
         <v>95</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
@@ -962,31 +962,31 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW2" t="n">
         <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
         <v>18.5</v>
@@ -995,46 +995,46 @@
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
         <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
@@ -1052,22 +1052,22 @@
         <v>70</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
         <v>6</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
         <v>2.28</v>
@@ -1150,19 +1150,19 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
         <v>17.5</v>
@@ -1177,13 +1177,13 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1219,122 +1219,122 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>5.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BH3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT3" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
         <v>6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1386,22 +1386,22 @@
         <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.38</v>
@@ -1413,25 +1413,25 @@
         <v>2.52</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1440,13 +1440,13 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
@@ -1455,10 +1455,10 @@
         <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
@@ -1467,118 +1467,118 @@
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT4" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AU4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4" t="n">
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>30</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>8</v>
@@ -1631,40 +1631,40 @@
         <v>1.67</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
         <v>2.48</v>
@@ -1676,10 +1676,10 @@
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>17</v>
@@ -1724,13 +1724,13 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AR5" t="n">
         <v>7.2</v>
@@ -1742,46 +1742,46 @@
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AV5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
         <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
         <v>2.5</v>
@@ -1790,34 +1790,34 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
         <v>2</v>
       </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BT5" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="BU5" t="n">
         <v>3.5</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -1873,175 +1873,175 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.85</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>21</v>
       </c>
-      <c r="AI6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC6" t="n">
         <v>13</v>
       </c>
-      <c r="BA6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
         <v>7.4</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BR6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>32</v>
       </c>
-      <c r="BS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>29</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I7" t="n">
         <v>2.64</v>
@@ -2238,13 +2238,13 @@
         <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
         <v>3.85</v>
@@ -2253,7 +2253,7 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>4.1</v>
@@ -2262,16 +2262,16 @@
         <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
@@ -2313,7 +2313,7 @@
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ7" t="n">
         <v>14</v>
@@ -2334,7 +2334,7 @@
         <v>18</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
         <v>26</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
         <v>2.58</v>
@@ -2659,10 +2659,10 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
         <v>1.75</v>
@@ -2674,10 +2674,10 @@
         <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2800,10 +2800,10 @@
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
         <v>7.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-07 22:47:48</t>
+          <t>2026-07-08 00:54:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -860,49 +860,49 @@
         <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V2" t="n">
         <v>1.58</v>
@@ -911,49 +911,49 @@
         <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK2" t="n">
         <v>95</v>
       </c>
-      <c r="AK2" t="n">
-        <v>70</v>
-      </c>
       <c r="AL2" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
@@ -962,125 +962,125 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>18.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
         <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
         <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>70</v>
+        <v>990</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>65</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -1111,28 +1111,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
         <v>2.92</v>
@@ -1141,34 +1141,34 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
         <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
@@ -1177,13 +1177,13 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1192,7 +1192,7 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
         <v>970</v>
@@ -1219,122 +1219,122 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
         <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AV3" t="n">
         <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>6.8</v>
+        <v>2.06</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X4" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5.1</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X4" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AV4" t="n">
-        <v>6.4</v>
+        <v>1.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>1.86</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>1.79</v>
       </c>
       <c r="AY4" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.4</v>
+        <v>1.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>1.86</v>
       </c>
       <c r="BB4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1637,40 +1637,40 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
         <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,10 +1679,10 @@
         <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
         <v>21</v>
@@ -1697,7 +1697,7 @@
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG5" t="n">
         <v>32</v>
@@ -1712,7 +1712,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="n">
         <v>150</v>
@@ -1721,16 +1721,16 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
         <v>7.2</v>
@@ -1739,49 +1739,49 @@
         <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX5" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX5" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>11</v>
-      </c>
       <c r="BH5" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
         <v>2.5</v>
@@ -1796,25 +1796,25 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.02</v>
+        <v>5.8</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.99</v>
+        <v>3.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="BT5" t="n">
         <v>3.95</v>
@@ -1823,26 +1823,26 @@
         <v>3.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.91</v>
+        <v>3.55</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
         <v>2.02</v>
       </c>
       <c r="H6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" t="n">
         <v>4.3</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1900,28 +1900,28 @@
         <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
         <v>1.98</v>
@@ -1936,16 +1936,16 @@
         <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1960,7 +1960,7 @@
         <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
         <v>23</v>
@@ -1978,13 +1978,13 @@
         <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
         <v>6.6</v>
@@ -1993,10 +1993,10 @@
         <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AV6" t="n">
         <v>5.9</v>
@@ -2005,43 +2005,43 @@
         <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="BA6" t="n">
         <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
         <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
         <v>7.4</v>
@@ -2053,25 +2053,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
         <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU6" t="n">
         <v>5.8</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BZ6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
@@ -2154,7 +2154,7 @@
         <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
         <v>2.34</v>
@@ -2166,19 +2166,19 @@
         <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
         <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
         <v>26</v>
@@ -2217,7 +2217,7 @@
         <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
         <v>34</v>
@@ -2232,61 +2232,61 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AS7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AY7" t="n">
         <v>3.85</v>
       </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="AZ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH7" t="n">
         <v>4.4</v>
@@ -2304,43 +2304,43 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS7" t="n">
         <v>20</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>19</v>
-      </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X8" t="n">
         <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
         <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -2456,40 +2456,40 @@
         <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2501,7 +2501,7 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2513,7 +2513,7 @@
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
         <v>7.8</v>
@@ -2537,22 +2537,22 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
         <v>48</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,50 +2561,50 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.7</v>
@@ -2650,49 +2650,49 @@
         <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
         <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>14</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>26</v>
@@ -2701,7 +2701,7 @@
         <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2800,7 +2800,7 @@
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2824,7 +2824,7 @@
         <v>21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN2" t="n">
         <v>150</v>
       </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
       </c>
       <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>210</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>15</v>
       </c>
-      <c r="AT2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BK2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW2" t="n">
         <v>23</v>
       </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>990</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="BZ2" t="n">
-        <v>960</v>
+        <v>110</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>65</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
         <v>48</v>
@@ -1177,13 +1177,13 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>960</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1195,7 +1195,7 @@
         <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1210,10 +1210,10 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
@@ -1222,16 +1222,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
         <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
@@ -1240,10 +1240,10 @@
         <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
@@ -1252,25 +1252,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
         <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="n">
         <v>3.1</v>
@@ -1306,10 +1306,10 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU3" t="n">
         <v>4.3</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.08</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM4" t="n">
         <v>500</v>
       </c>
-      <c r="Y4" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.89</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.81</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.84</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.87</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.75</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.86</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.86</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.82</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.82</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.88</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY4" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="I5" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1643,151 +1643,151 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
         <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>270</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK5" t="n">
         <v>8.800000000000001</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
@@ -1888,10 +1888,10 @@
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1912,7 +1912,7 @@
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1924,7 +1924,7 @@
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X6" t="n">
         <v>17.5</v>
@@ -2035,13 +2035,13 @@
         <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
         <v>7.4</v>
@@ -2053,25 +2053,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
         <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
         <v>5.8</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2154,19 +2154,19 @@
         <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
         <v>1.55</v>
@@ -2175,16 +2175,16 @@
         <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
@@ -2214,10 +2214,10 @@
         <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
         <v>34</v>
@@ -2229,61 +2229,61 @@
         <v>75</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR7" t="n">
         <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
         <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
         <v>3.85</v>
@@ -2304,40 +2304,40 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BR7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.41</v>
@@ -2405,34 +2405,34 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
         <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
         <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
         <v>17</v>
@@ -2504,7 +2504,7 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>12.5</v>
@@ -2543,16 +2543,16 @@
         <v>48</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,7 +2564,7 @@
         <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
         <v>14</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
         <v>3.25</v>
@@ -2653,7 +2653,7 @@
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2662,13 +2662,13 @@
         <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
@@ -2686,7 +2686,7 @@
         <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
@@ -2734,7 +2734,7 @@
         <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
@@ -2800,7 +2800,7 @@
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2833,13 +2833,13 @@
         <v>27</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
         <v>5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
         <v>22</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>470</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>880</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1.26</v>
       </c>
-      <c r="S2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>800</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.2</v>
+        <v>1.06</v>
       </c>
       <c r="BO2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
         <v>3.15</v>
@@ -1129,43 +1129,43 @@
         <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
         <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y3" t="n">
         <v>18.5</v>
@@ -1177,10 +1177,10 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
@@ -1210,16 +1210,16 @@
         <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP3" t="n">
         <v>22</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
       </c>
       <c r="AQ3" t="n">
         <v>16</v>
@@ -1228,7 +1228,7 @@
         <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1237,10 +1237,10 @@
         <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1249,28 +1249,28 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
         <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.4</v>
@@ -1282,13 +1282,13 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>5.5</v>
@@ -1297,16 +1297,16 @@
         <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>23</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>6.8</v>
@@ -1315,16 +1315,16 @@
         <v>5.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1368,37 @@
         <v>6.8</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
@@ -1407,13 +1407,13 @@
         <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
@@ -1425,16 +1425,16 @@
         <v>6.6</v>
       </c>
       <c r="Z4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>10.5</v>
@@ -1449,13 +1449,13 @@
         <v>28</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AK4" t="n">
         <v>140</v>
@@ -1464,16 +1464,16 @@
         <v>150</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN4" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
         <v>6</v>
@@ -1482,55 +1482,55 @@
         <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
         <v>46</v>
       </c>
       <c r="AY4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,53 +1542,53 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
         <v>13</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
@@ -1619,178 +1619,178 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
       </c>
       <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="AR5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
         <v>14</v>
       </c>
-      <c r="AO5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>15</v>
-      </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF5" t="n">
         <v>14</v>
       </c>
-      <c r="BD5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>10</v>
-      </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BT5" t="n">
         <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I6" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.29</v>
@@ -1897,34 +1897,34 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
         <v>26</v>
@@ -1936,7 +1936,7 @@
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
         <v>19</v>
@@ -1945,7 +1945,7 @@
         <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1957,7 +1957,7 @@
         <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>34</v>
@@ -1966,13 +1966,13 @@
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
         <v>22</v>
@@ -1981,70 +1981,70 @@
         <v>14.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BI6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>50</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BZ6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
@@ -2127,28 +2127,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H7" t="n">
         <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>3.85</v>
@@ -2157,13 +2157,13 @@
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
         <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
         <v>3.55</v>
@@ -2172,13 +2172,13 @@
         <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X7" t="n">
         <v>17</v>
@@ -2190,109 +2190,109 @@
         <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>21</v>
       </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
         <v>130</v>
       </c>
       <c r="AN7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AW7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF7" t="n">
         <v>11</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="n">
         <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2310,22 +2310,22 @@
         <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP7" t="n">
         <v>14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
         <v>19.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
         <v>5.9</v>
@@ -2334,7 +2334,7 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2343,21 +2343,21 @@
         <v>32</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,222 +2367,222 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rhode Island FC</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.26</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.66</v>
-      </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AW8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO8" t="n">
+      <c r="BD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>50</v>
       </c>
-      <c r="AP8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BN8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BT8" t="n">
+      <c r="BU8" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5</v>
       </c>
       <c r="BV8" t="n">
         <v>32</v>
@@ -2591,20 +2591,274 @@
         <v>22</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>32</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>27</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-08 07:13:04</t>
+      <c r="BZ9" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jiangxi Lushan</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.7</v>
       </c>
-      <c r="I2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.86</v>
       </c>
       <c r="S2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X2" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH2" t="n">
         <v>5.3</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>470</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>880</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>290</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI2" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>800</v>
+        <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP2" t="n">
         <v>13.5</v>
       </c>
-      <c r="BN2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>800</v>
-      </c>
       <c r="BQ2" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI3" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X3" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BJ3" t="n">
         <v>12</v>
       </c>
-      <c r="AU3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Sarasota Paradise</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.8</v>
       </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AV4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>18</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BA4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB4" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
         <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>85</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BH4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.3</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG5" t="n">
         <v>15</v>
       </c>
-      <c r="Y5" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>18.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>65</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>46</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY5" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Hartford Athletic FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="H6" t="n">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.85</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>26</v>
       </c>
-      <c r="Y6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM6" t="n">
+      <c r="BE6" t="n">
         <v>80</v>
       </c>
-      <c r="AN6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="BF6" t="n">
         <v>11</v>
       </c>
-      <c r="AR6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV6" t="n">
         <v>1000</v>
       </c>
-      <c r="BS6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>17</v>
-      </c>
       <c r="BW6" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>16.5</v>
       </c>
-      <c r="CA6" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
         <v>17</v>
       </c>
-      <c r="Y7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD7" t="n">
         <v>21</v>
       </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>27</v>
-      </c>
       <c r="BE7" t="n">
-        <v>80</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>40</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BS7" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>26</v>
-      </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY7" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,222 +2367,222 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boliviano</t>
+          <t>Rhode Island FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
         <v>18</v>
       </c>
-      <c r="AI8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="BG8" t="n">
         <v>32</v>
       </c>
-      <c r="AX8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH8" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>32</v>
@@ -2591,274 +2591,20 @@
         <v>22</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Rhode Island FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>25</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S2" t="n">
         <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="U2" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
         <v>1.86</v>
@@ -914,22 +914,22 @@
         <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
         <v>50</v>
@@ -944,28 +944,28 @@
         <v>14.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
       </c>
       <c r="AL2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
@@ -974,10 +974,10 @@
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
         <v>17.5</v>
@@ -1010,31 +1010,31 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>5.9</v>
@@ -1046,31 +1046,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>7.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
         <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1111,34 +1111,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="G3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
         <v>1.73</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1.68</v>
@@ -1153,7 +1153,7 @@
         <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
         <v>1.76</v>
@@ -1162,91 +1162,91 @@
         <v>2.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
         <v>6.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB3" t="n">
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AK3" t="n">
         <v>130</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM3" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
         <v>210</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
         <v>14.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1255,19 +1255,19 @@
         <v>46</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>14</v>
-      </c>
       <c r="BF3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
         <v>13.5</v>
@@ -1276,37 +1276,37 @@
         <v>2.98</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BP3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BS3" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>22</v>
       </c>
       <c r="BT3" t="n">
         <v>4</v>
@@ -1315,26 +1315,26 @@
         <v>3.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1368,175 +1368,175 @@
         <v>2.02</v>
       </c>
       <c r="G4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.06</v>
       </c>
-      <c r="H4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>38</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB4" t="n">
         <v>18.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
         <v>5.4</v>
@@ -1649,142 +1649,142 @@
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
         <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
         <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
         <v>60</v>
       </c>
       <c r="AN5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY5" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH5" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BI5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1823,26 +1823,26 @@
         <v>4.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>13.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY5" t="n">
         <v>18</v>
       </c>
       <c r="BZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1906,16 +1906,16 @@
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
         <v>2.02</v>
@@ -1924,16 +1924,16 @@
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
         <v>120</v>
@@ -1978,22 +1978,22 @@
         <v>13.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -2002,7 +2002,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -2011,34 +2011,34 @@
         <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB6" t="n">
         <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2056,7 +2056,7 @@
         <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP6" t="n">
         <v>14</v>
@@ -2065,7 +2065,7 @@
         <v>9.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
         <v>19.5</v>
@@ -2080,7 +2080,7 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
@@ -2142,25 +2142,25 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
         <v>1.68</v>
@@ -2178,7 +2178,7 @@
         <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
         <v>32</v>
@@ -2220,7 +2220,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>27</v>
@@ -2235,16 +2235,16 @@
         <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2268,7 +2268,7 @@
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -2280,7 +2280,7 @@
         <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
         <v>5.4</v>
@@ -2289,58 +2289,58 @@
         <v>6.4</v>
       </c>
       <c r="BH7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK7" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP7" t="n">
         <v>9.6</v>
       </c>
-      <c r="BN7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>11</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BS7" t="n">
         <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX7" t="n">
         <v>34</v>
       </c>
-      <c r="BW7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>36</v>
-      </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
@@ -2393,40 +2393,40 @@
         <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
         <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.4</v>
@@ -2435,124 +2435,124 @@
         <v>1.66</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>40</v>
       </c>
       <c r="AK8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN8" t="n">
         <v>34</v>
       </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>27</v>
-      </c>
       <c r="AO8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2567,10 +2567,10 @@
         <v>4.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>32</v>
       </c>
       <c r="BZ8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
         <v>3.35</v>
@@ -881,46 +881,46 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>19.5</v>
@@ -932,22 +932,22 @@
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
@@ -962,22 +962,22 @@
         <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AR2" t="n">
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -1010,7 +1010,7 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -1058,7 +1058,7 @@
         <v>7.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.71</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.73</v>
-      </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.16</v>
@@ -1171,10 +1171,10 @@
         <v>6.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB3" t="n">
         <v>17</v>
@@ -1186,22 +1186,22 @@
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AK3" t="n">
         <v>130</v>
@@ -1216,22 +1216,22 @@
         <v>210</v>
       </c>
       <c r="AO3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
         <v>14.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1240,101 +1240,101 @@
         <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
         <v>46</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI3" t="n">
         <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BN3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO3" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BS3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY3" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1365,52 +1365,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
         <v>2.12</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V4" t="n">
         <v>1.27</v>
@@ -1419,176 +1419,176 @@
         <v>1.89</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="n">
         <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
         <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="BF4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO4" t="n">
         <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1643,28 +1643,28 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
@@ -1673,7 +1673,7 @@
         <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
         <v>19.5</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
@@ -1760,19 +1760,19 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
@@ -1781,22 +1781,22 @@
         <v>11.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1805,44 +1805,44 @@
         <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY5" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1897,37 +1897,37 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>17</v>
@@ -1936,19 +1936,19 @@
         <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
         <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>18.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1960,25 +1960,25 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>12.5</v>
@@ -1987,13 +1987,13 @@
         <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -2020,16 +2020,16 @@
         <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE6" t="n">
         <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
         <v>34</v>
@@ -2038,19 +2038,19 @@
         <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2059,44 +2059,44 @@
         <v>3.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
         <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
         <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X7" t="n">
         <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
         <v>48</v>
@@ -2223,10 +2223,10 @@
         <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
         <v>7.2</v>
@@ -2235,31 +2235,31 @@
         <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7" t="n">
         <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
@@ -2268,79 +2268,79 @@
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC7" t="n">
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BR7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BS7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7</v>
       </c>
-      <c r="BT7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BX7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -2381,109 +2381,109 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>60</v>
@@ -2495,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2519,16 +2519,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
         <v>30</v>
@@ -2537,74 +2537,74 @@
         <v>38</v>
       </c>
       <c r="BF8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,88 +857,88 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.08</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
         <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
@@ -947,85 +947,85 @@
         <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10</v>
-      </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK2" t="n">
         <v>5.4</v>
@@ -1037,40 +1037,40 @@
         <v>12</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BS2" t="n">
         <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -1135,19 +1135,19 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
         <v>4.6</v>
@@ -1159,28 +1159,28 @@
         <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z3" t="n">
         <v>8.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
@@ -1189,10 +1189,10 @@
         <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -1204,34 +1204,34 @@
         <v>250</v>
       </c>
       <c r="AK3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL3" t="n">
         <v>130</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>140</v>
       </c>
       <c r="AM3" t="n">
         <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AO3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
         <v>14.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1240,43 +1240,43 @@
         <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AY3" t="n">
         <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BP3" t="n">
         <v>75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BR3" t="n">
         <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BT3" t="n">
         <v>3.9</v>
@@ -1315,10 +1315,10 @@
         <v>3.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>34</v>
@@ -1330,11 +1330,11 @@
         <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1365,52 +1365,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.27</v>
@@ -1419,115 +1419,115 @@
         <v>1.89</v>
       </c>
       <c r="X4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y4" t="n">
-        <v>13</v>
-      </c>
       <c r="Z4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
         <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
         <v>16</v>
       </c>
-      <c r="AW4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI4" t="n">
         <v>2.52</v>
@@ -1536,59 +1536,59 @@
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
         <v>16</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H5" t="n">
         <v>2.64</v>
@@ -1631,40 +1631,40 @@
         <v>2.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
@@ -1673,85 +1673,85 @@
         <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK5" t="n">
         <v>32</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
       <c r="AL5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS5" t="n">
         <v>32</v>
       </c>
-      <c r="AM5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
@@ -1760,37 +1760,37 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,16 +1799,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
@@ -1817,32 +1817,32 @@
         <v>7</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
         <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA5" t="n">
         <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
@@ -1885,46 +1885,46 @@
         <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1933,13 +1933,13 @@
         <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
         <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>9.4</v>
@@ -1948,19 +1948,19 @@
         <v>18.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
@@ -1978,22 +1978,22 @@
         <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -2005,13 +2005,13 @@
         <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
         <v>38</v>
@@ -2023,34 +2023,34 @@
         <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2062,16 +2062,16 @@
         <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU6" t="n">
         <v>6</v>
@@ -2080,23 +2080,23 @@
         <v>38</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -2127,76 +2127,76 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Z7" t="n">
         <v>48</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
         <v>25</v>
@@ -2205,142 +2205,142 @@
         <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>26</v>
       </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO7" t="n">
         <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BM7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT7" t="n">
         <v>11</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H8" t="n">
         <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.47</v>
@@ -2411,7 +2411,7 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
         <v>2.16</v>
@@ -2423,16 +2423,16 @@
         <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2444,7 +2444,7 @@
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
         <v>9.4</v>
@@ -2471,7 +2471,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2489,13 +2489,13 @@
         <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
         <v>50</v>
@@ -2504,13 +2504,13 @@
         <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="n">
         <v>12</v>
@@ -2552,59 +2552,59 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R2" t="n">
         <v>2.04</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.93</v>
-      </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="T2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO2" t="n">
         <v>34</v>
       </c>
-      <c r="AA2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BG2" t="n">
         <v>25</v>
       </c>
-      <c r="AR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BH2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1111,82 +1111,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="I3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
         <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
         <v>65</v>
@@ -1195,28 +1195,28 @@
         <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AK3" t="n">
         <v>140</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM3" t="n">
         <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
         <v>10.5</v>
@@ -1228,7 +1228,7 @@
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
         <v>17</v>
@@ -1237,13 +1237,13 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AY3" t="n">
         <v>24</v>
@@ -1252,70 +1252,70 @@
         <v>25</v>
       </c>
       <c r="BA3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC3" t="n">
         <v>48</v>
       </c>
-      <c r="BB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>16.5</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15.5</v>
+        <v>160</v>
       </c>
       <c r="BN3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BQ3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW3" t="n">
         <v>10</v>
@@ -1324,17 +1324,17 @@
         <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.64</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.89</v>
       </c>
       <c r="X4" t="n">
         <v>11</v>
       </c>
       <c r="Y4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>36</v>
       </c>
-      <c r="AA4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
         <v>11</v>
       </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE4" t="n">
         <v>100</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BF4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>10</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD4" t="n">
+      <c r="BK4" t="n">
         <v>9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS4" t="n">
         <v>12</v>
       </c>
-      <c r="BN4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BT4" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
         <v>1.52</v>
@@ -1658,97 +1658,97 @@
         <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.51</v>
       </c>
       <c r="U5" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>29</v>
       </c>
-      <c r="AA5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>38</v>
-      </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS5" t="n">
         <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>32</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,89 +1760,89 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
         <v>6.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW5" t="n">
         <v>7</v>
       </c>
-      <c r="BT5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.95</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
@@ -1906,197 +1906,197 @@
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
         <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
         <v>44</v>
       </c>
-      <c r="AM6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>38</v>
-      </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
         <v>70</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
         <v>32</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY6" t="n">
         <v>11</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW6" t="n">
+      <c r="BZ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2127,184 +2127,184 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
         <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="X7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW7" t="n">
         <v>34</v>
       </c>
-      <c r="Y7" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AX7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BI7" t="n">
         <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="BN7" t="n">
         <v>5.5</v>
@@ -2313,34 +2313,34 @@
         <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW7" t="n">
         <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
@@ -2402,28 +2402,28 @@
         <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
@@ -2432,7 +2432,7 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2453,10 +2453,10 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>14.5</v>
@@ -2471,7 +2471,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2483,10 +2483,10 @@
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
@@ -2504,7 +2504,7 @@
         <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>12.5</v>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>22</v>
@@ -2540,71 +2540,71 @@
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
         <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,78 +843,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarasota Paradise</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>2.98</v>
+        <v>1.05</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -923,100 +923,100 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BA2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Hartford Athletic FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>8.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>960</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>1.14</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>1.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>850</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>970</v>
       </c>
       <c r="AN4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>1.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="H5" t="n">
-        <v>2.86</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="K5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W5" t="n">
         <v>4.2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.68</v>
-      </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI5" t="n">
         <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>18.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -1859,752 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hartford Athletic FC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Rhode Island FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.06</v>
       </c>
-      <c r="H6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.18</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>470</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AQ6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AR6" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA6" t="n">
         <v>9</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>44</v>
-      </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
         <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Real Potosi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Academia de Balompie Boliviano</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>60</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-07-08 19:58:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Rhode Island FC</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
